--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/118.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/118.xlsx
@@ -426,13 +426,13 @@
         <v>-9.449415172751065</v>
       </c>
       <c r="E2">
-        <v>-21.68964005400765</v>
+        <v>-20.46005067754896</v>
       </c>
       <c r="F2">
-        <v>-0.3948124769327941</v>
+        <v>-0.5834350480198528</v>
       </c>
       <c r="G2">
-        <v>-14.03240046827466</v>
+        <v>-12.75325069615151</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.964252350059967</v>
       </c>
       <c r="E3">
-        <v>-21.31275327624527</v>
+        <v>-19.69254678883296</v>
       </c>
       <c r="F3">
-        <v>-0.03666120339320547</v>
+        <v>0.191699808740951</v>
       </c>
       <c r="G3">
-        <v>-14.07934818634719</v>
+        <v>-12.26157605157652</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.435143869661951</v>
       </c>
       <c r="E4">
-        <v>-22.63300270233752</v>
+        <v>-19.16483012729711</v>
       </c>
       <c r="F4">
-        <v>-0.2902228086553286</v>
+        <v>0.1636471466451458</v>
       </c>
       <c r="G4">
-        <v>-13.60920655825606</v>
+        <v>-11.30618933255612</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.923207048917197</v>
       </c>
       <c r="E5">
-        <v>-22.58076222618503</v>
+        <v>-18.9828715131949</v>
       </c>
       <c r="F5">
-        <v>0.08533577748668891</v>
+        <v>-0.4652054820878905</v>
       </c>
       <c r="G5">
-        <v>-13.09306384451228</v>
+        <v>-11.90786036746838</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.435939702309004</v>
       </c>
       <c r="E6">
-        <v>-22.92983058811829</v>
+        <v>-21.04088633919478</v>
       </c>
       <c r="F6">
-        <v>0.05061889963536164</v>
+        <v>-0.1165365302081478</v>
       </c>
       <c r="G6">
-        <v>-12.76002641867176</v>
+        <v>-11.62606905994327</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.001567178312762</v>
       </c>
       <c r="E7">
-        <v>-24.88015830221577</v>
+        <v>-22.56459104550364</v>
       </c>
       <c r="F7">
-        <v>-0.09938601150058683</v>
+        <v>0.4609871407778199</v>
       </c>
       <c r="G7">
-        <v>-12.41478284863011</v>
+        <v>-10.70553547632729</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.624482176190843</v>
       </c>
       <c r="E8">
-        <v>-23.92920140297503</v>
+        <v>-22.04073717229634</v>
       </c>
       <c r="F8">
-        <v>0.1388466549727314</v>
+        <v>0.302427679473161</v>
       </c>
       <c r="G8">
-        <v>-12.16107879765385</v>
+        <v>-11.57667026936583</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.317636195379437</v>
       </c>
       <c r="E9">
-        <v>-24.31194349762932</v>
+        <v>-22.62126489770964</v>
       </c>
       <c r="F9">
-        <v>0.1741218524535455</v>
+        <v>-0.02987687436427752</v>
       </c>
       <c r="G9">
-        <v>-12.21942876064545</v>
+        <v>-10.78472119622137</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.074935514523807</v>
       </c>
       <c r="E10">
-        <v>-24.96389884356561</v>
+        <v>-23.25118921759861</v>
       </c>
       <c r="F10">
-        <v>0.3683251347332644</v>
+        <v>0.3241748088988564</v>
       </c>
       <c r="G10">
-        <v>-11.84617668337238</v>
+        <v>-11.25417868961736</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.893460525916884</v>
       </c>
       <c r="E11">
-        <v>-25.16655711235687</v>
+        <v>-23.34955672999322</v>
       </c>
       <c r="F11">
-        <v>0.6411645061933375</v>
+        <v>0.9863741957989896</v>
       </c>
       <c r="G11">
-        <v>-11.85206647607158</v>
+        <v>-10.48995265742865</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.762345540093893</v>
       </c>
       <c r="E12">
-        <v>-25.74014721559042</v>
+        <v>-24.66477502146295</v>
       </c>
       <c r="F12">
-        <v>0.7474249915222497</v>
+        <v>0.3694807072601697</v>
       </c>
       <c r="G12">
-        <v>-10.49335200296424</v>
+        <v>-9.549626745366103</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.664839437017181</v>
       </c>
       <c r="E13">
-        <v>-26.99427186422266</v>
+        <v>-25.49850331406712</v>
       </c>
       <c r="F13">
-        <v>0.8479274950343025</v>
+        <v>0.4943430109863476</v>
       </c>
       <c r="G13">
-        <v>-11.16849615103558</v>
+        <v>-10.02865884327256</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.589847431457097</v>
       </c>
       <c r="E14">
-        <v>-28.23141926380015</v>
+        <v>-25.4816619192326</v>
       </c>
       <c r="F14">
-        <v>1.400851139259333</v>
+        <v>1.27216426323443</v>
       </c>
       <c r="G14">
-        <v>-10.30572519175207</v>
+        <v>-8.75333989732006</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.517924832265332</v>
       </c>
       <c r="E15">
-        <v>-27.91322150917719</v>
+        <v>-27.44632225356435</v>
       </c>
       <c r="F15">
-        <v>1.588878942551182</v>
+        <v>1.134517765380848</v>
       </c>
       <c r="G15">
-        <v>-10.57453926800958</v>
+        <v>-8.794830943939239</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.44163182725499</v>
       </c>
       <c r="E16">
-        <v>-29.57243627169158</v>
+        <v>-25.95183526155298</v>
       </c>
       <c r="F16">
-        <v>2.067910557711691</v>
+        <v>1.644232109141051</v>
       </c>
       <c r="G16">
-        <v>-10.43670171274042</v>
+        <v>-9.293330529357876</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.352769646150625</v>
       </c>
       <c r="E17">
-        <v>-29.56804818037814</v>
+        <v>-26.66524652824736</v>
       </c>
       <c r="F17">
-        <v>2.071984468598659</v>
+        <v>2.478586951527991</v>
       </c>
       <c r="G17">
-        <v>-9.974643373960978</v>
+        <v>-8.477389164170759</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.252589379576949</v>
       </c>
       <c r="E18">
-        <v>-31.54211415522383</v>
+        <v>-28.34057812975504</v>
       </c>
       <c r="F18">
-        <v>2.261082522574925</v>
+        <v>1.997631867258181</v>
       </c>
       <c r="G18">
-        <v>-9.71125643816279</v>
+        <v>-9.335041417821538</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.143846654313498</v>
       </c>
       <c r="E19">
-        <v>-31.23495229175755</v>
+        <v>-29.15954812556822</v>
       </c>
       <c r="F19">
-        <v>2.487814964395178</v>
+        <v>2.028614464857688</v>
       </c>
       <c r="G19">
-        <v>-9.968707644159942</v>
+        <v>-8.730558376032835</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.029070614361411</v>
       </c>
       <c r="E20">
-        <v>-32.03651709772225</v>
+        <v>-28.5118223743551</v>
       </c>
       <c r="F20">
-        <v>2.841660384175014</v>
+        <v>2.954578458320226</v>
       </c>
       <c r="G20">
-        <v>-9.916175286993232</v>
+        <v>-8.476076675546981</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.91553352204498</v>
       </c>
       <c r="E21">
-        <v>-32.41382049509333</v>
+        <v>-30.14227906268378</v>
       </c>
       <c r="F21">
-        <v>3.224664336533394</v>
+        <v>3.121477922636271</v>
       </c>
       <c r="G21">
-        <v>-10.64316929814692</v>
+        <v>-8.555108178027767</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.804027361343214</v>
       </c>
       <c r="E22">
-        <v>-33.18076285303238</v>
+        <v>-29.41106862890225</v>
       </c>
       <c r="F22">
-        <v>3.075437262388674</v>
+        <v>2.331049746884982</v>
       </c>
       <c r="G22">
-        <v>-9.46650684082225</v>
+        <v>-7.972793069094672</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.698602292067634</v>
       </c>
       <c r="E23">
-        <v>-32.21419856812421</v>
+        <v>-32.31105809867427</v>
       </c>
       <c r="F23">
-        <v>3.417337624220142</v>
+        <v>3.924845197219287</v>
       </c>
       <c r="G23">
-        <v>-10.19691988484088</v>
+        <v>-8.825011619843011</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.597251184437549</v>
       </c>
       <c r="E24">
-        <v>-33.34780014527931</v>
+        <v>-30.6591771998153</v>
       </c>
       <c r="F24">
-        <v>3.891158808417043</v>
+        <v>3.332857403013037</v>
       </c>
       <c r="G24">
-        <v>-9.658366427846101</v>
+        <v>-7.369589703714153</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.500817326824204</v>
       </c>
       <c r="E25">
-        <v>-32.89495274451227</v>
+        <v>-32.77467873910555</v>
       </c>
       <c r="F25">
-        <v>3.062769868065064</v>
+        <v>3.342642078774905</v>
       </c>
       <c r="G25">
-        <v>-9.987197327647413</v>
+        <v>-7.387495329764043</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.40907928104766</v>
       </c>
       <c r="E26">
-        <v>-33.50443779696762</v>
+        <v>-32.5061945721388</v>
       </c>
       <c r="F26">
-        <v>3.218658672863097</v>
+        <v>3.884912918199934</v>
       </c>
       <c r="G26">
-        <v>-9.422243161985341</v>
+        <v>-8.257603100454475</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.322007119061752</v>
       </c>
       <c r="E27">
-        <v>-33.45502761706993</v>
+        <v>-31.95587403259366</v>
       </c>
       <c r="F27">
-        <v>3.44257135204422</v>
+        <v>3.433411265304064</v>
       </c>
       <c r="G27">
-        <v>-10.12342380313088</v>
+        <v>-8.648839553094865</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.243508349059786</v>
       </c>
       <c r="E28">
-        <v>-32.42424277802198</v>
+        <v>-32.75088387243225</v>
       </c>
       <c r="F28">
-        <v>3.137863029863645</v>
+        <v>3.72657380262442</v>
       </c>
       <c r="G28">
-        <v>-9.474440834552986</v>
+        <v>-7.54232633148956</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.173829951197383</v>
       </c>
       <c r="E29">
-        <v>-33.2254679484361</v>
+        <v>-31.51381345691289</v>
       </c>
       <c r="F29">
-        <v>3.102052707040622</v>
+        <v>3.036270394849508</v>
       </c>
       <c r="G29">
-        <v>-9.803009236629544</v>
+        <v>-8.252563144139167</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.117667326109153</v>
       </c>
       <c r="E30">
-        <v>-31.83657364909859</v>
+        <v>-31.20276842698504</v>
       </c>
       <c r="F30">
-        <v>2.838742874182354</v>
+        <v>3.444524642380022</v>
       </c>
       <c r="G30">
-        <v>-9.353324384350763</v>
+        <v>-7.319744667004628</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.075491984196479</v>
       </c>
       <c r="E31">
-        <v>-32.58476133193487</v>
+        <v>-32.37875652085194</v>
       </c>
       <c r="F31">
-        <v>2.738811944178233</v>
+        <v>3.262610190520833</v>
       </c>
       <c r="G31">
-        <v>-8.865830016042503</v>
+        <v>-8.299625704966282</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.049463947684628</v>
       </c>
       <c r="E32">
-        <v>-32.56083287527834</v>
+        <v>-30.84591108975859</v>
       </c>
       <c r="F32">
-        <v>2.44336311282615</v>
+        <v>2.884624487888614</v>
       </c>
       <c r="G32">
-        <v>-8.810026280981027</v>
+        <v>-7.080333617141304</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.039223077305089</v>
       </c>
       <c r="E33">
-        <v>-31.91972775306443</v>
+        <v>-29.81377676545636</v>
       </c>
       <c r="F33">
-        <v>2.42860657591268</v>
+        <v>2.654886729131004</v>
       </c>
       <c r="G33">
-        <v>-8.454328739050982</v>
+        <v>-7.36098305956373</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.040860091848329</v>
       </c>
       <c r="E34">
-        <v>-31.46409307654568</v>
+        <v>-28.80111487938711</v>
       </c>
       <c r="F34">
-        <v>2.408770490085243</v>
+        <v>3.078348145442111</v>
       </c>
       <c r="G34">
-        <v>-9.087830904311414</v>
+        <v>-8.073234542250834</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.050539302576301</v>
       </c>
       <c r="E35">
-        <v>-30.50873902904349</v>
+        <v>-29.00893108007311</v>
       </c>
       <c r="F35">
-        <v>2.529591189253162</v>
+        <v>2.582378073629158</v>
       </c>
       <c r="G35">
-        <v>-8.84900719310723</v>
+        <v>-8.226713680693861</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.056934799124822</v>
       </c>
       <c r="E36">
-        <v>-30.56586799288726</v>
+        <v>-29.00637702073278</v>
       </c>
       <c r="F36">
-        <v>2.555587015087816</v>
+        <v>3.2797623659632</v>
       </c>
       <c r="G36">
-        <v>-9.016608709142107</v>
+        <v>-7.252538687024082</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.049828533732451</v>
       </c>
       <c r="E37">
-        <v>-29.55427256244681</v>
+        <v>-29.51226417331466</v>
       </c>
       <c r="F37">
-        <v>2.444600693725933</v>
+        <v>3.081161281142018</v>
       </c>
       <c r="G37">
-        <v>-8.686094542680801</v>
+        <v>-6.64769471086384</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.01604807018585</v>
       </c>
       <c r="E38">
-        <v>-28.02202715415948</v>
+        <v>-26.59451629272155</v>
       </c>
       <c r="F38">
-        <v>2.728101153660035</v>
+        <v>2.862929545609294</v>
       </c>
       <c r="G38">
-        <v>-8.575281128175233</v>
+        <v>-7.580053816980056</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.943667624258754</v>
       </c>
       <c r="E39">
-        <v>-28.45530701873938</v>
+        <v>-25.88866304914598</v>
       </c>
       <c r="F39">
-        <v>2.535964648050302</v>
+        <v>3.130170810161248</v>
       </c>
       <c r="G39">
-        <v>-8.14193019681937</v>
+        <v>-8.352144937246754</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.825540562909273</v>
       </c>
       <c r="E40">
-        <v>-28.44422584284261</v>
+        <v>-26.2850630214074</v>
       </c>
       <c r="F40">
-        <v>2.312911814233284</v>
+        <v>3.16673826079043</v>
       </c>
       <c r="G40">
-        <v>-8.712091661096281</v>
+        <v>-7.69578906382479</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.653640916215409</v>
       </c>
       <c r="E41">
-        <v>-28.74308701345282</v>
+        <v>-26.25183307913912</v>
       </c>
       <c r="F41">
-        <v>2.490913058481647</v>
+        <v>2.361570115473727</v>
       </c>
       <c r="G41">
-        <v>-8.754882071452998</v>
+        <v>-8.711107294628446</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.429131673041955</v>
       </c>
       <c r="E42">
-        <v>-28.20134566791521</v>
+        <v>-24.98174555962984</v>
       </c>
       <c r="F42">
-        <v>2.389961579837277</v>
+        <v>2.820702688884187</v>
       </c>
       <c r="G42">
-        <v>-8.939454065393324</v>
+        <v>-7.923827399763079</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.15320129512767</v>
       </c>
       <c r="E43">
-        <v>-26.88563830125266</v>
+        <v>-26.16328329839313</v>
       </c>
       <c r="F43">
-        <v>2.229119137970503</v>
+        <v>3.178035535429809</v>
       </c>
       <c r="G43">
-        <v>-8.612339244467602</v>
+        <v>-8.124464254458445</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.834538344270105</v>
       </c>
       <c r="E44">
-        <v>-26.36716425516646</v>
+        <v>-25.55495979952075</v>
       </c>
       <c r="F44">
-        <v>2.339510691537176</v>
+        <v>2.150500444505608</v>
       </c>
       <c r="G44">
-        <v>-8.28929641949715</v>
+        <v>-8.111660927933492</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.48506493179767</v>
       </c>
       <c r="E45">
-        <v>-26.40404414748493</v>
+        <v>-25.96894836482797</v>
       </c>
       <c r="F45">
-        <v>2.428492261211094</v>
+        <v>1.967432905221723</v>
       </c>
       <c r="G45">
-        <v>-9.245795472626201</v>
+        <v>-6.791018468580385</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.116437900687564</v>
       </c>
       <c r="E46">
-        <v>-25.23621862801686</v>
+        <v>-23.32635282917792</v>
       </c>
       <c r="F46">
-        <v>2.276579619946498</v>
+        <v>3.090559937694182</v>
       </c>
       <c r="G46">
-        <v>-8.363737493016272</v>
+        <v>-7.235496022244326</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.746183614892679</v>
       </c>
       <c r="E47">
-        <v>-25.65412432334071</v>
+        <v>-25.50649607069066</v>
       </c>
       <c r="F47">
-        <v>2.296506826188243</v>
+        <v>2.337545804057736</v>
       </c>
       <c r="G47">
-        <v>-8.710227927250516</v>
+        <v>-7.20427191788465</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.385365175689877</v>
       </c>
       <c r="E48">
-        <v>-24.95323881575155</v>
+        <v>-23.0562384115684</v>
       </c>
       <c r="F48">
-        <v>2.305711644768151</v>
+        <v>3.222200771877468</v>
       </c>
       <c r="G48">
-        <v>-8.809763783256271</v>
+        <v>-7.312178170088549</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.04896208912953</v>
       </c>
       <c r="E49">
-        <v>-24.95626836486268</v>
+        <v>-22.68599943364929</v>
       </c>
       <c r="F49">
-        <v>2.52109545317005</v>
+        <v>2.384088454951429</v>
       </c>
       <c r="G49">
-        <v>-7.87329658774763</v>
+        <v>-7.937674154743935</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.7458575447941271</v>
       </c>
       <c r="E50">
-        <v>-23.96145319485766</v>
+        <v>-21.79568332984526</v>
       </c>
       <c r="F50">
-        <v>2.080042826693093</v>
+        <v>2.790202201113109</v>
       </c>
       <c r="G50">
-        <v>-8.797754512348703</v>
+        <v>-9.050415134869066</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.4854967104082237</v>
       </c>
       <c r="E51">
-        <v>-23.72391209078531</v>
+        <v>-20.72677779660074</v>
       </c>
       <c r="F51">
-        <v>2.46543413390634</v>
+        <v>2.709641814456051</v>
       </c>
       <c r="G51">
-        <v>-9.339674502663474</v>
+        <v>-7.795318357387426</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.27543451927821</v>
       </c>
       <c r="E52">
-        <v>-23.44013073862064</v>
+        <v>-22.25148782413931</v>
       </c>
       <c r="F52">
-        <v>2.641359489443288</v>
+        <v>3.095402573530948</v>
       </c>
       <c r="G52">
-        <v>-8.645131772732691</v>
+        <v>-7.929103604030666</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.1188841789585488</v>
       </c>
       <c r="E53">
-        <v>-22.5023381133202</v>
+        <v>-21.29142869214315</v>
       </c>
       <c r="F53">
-        <v>2.512982422827032</v>
+        <v>2.285650243007153</v>
       </c>
       <c r="G53">
-        <v>-9.253017441278539</v>
+        <v>-7.600131611702298</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.01985270835593414</v>
       </c>
       <c r="E54">
-        <v>-22.434329490673</v>
+        <v>-19.74415327862437</v>
       </c>
       <c r="F54">
-        <v>2.176597331163403</v>
+        <v>2.140387735252231</v>
       </c>
       <c r="G54">
-        <v>-9.686614464251361</v>
+        <v>-6.51923160559002</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>0.02433766402655275</v>
       </c>
       <c r="E55">
-        <v>-21.72740299875761</v>
+        <v>-20.11799239337958</v>
       </c>
       <c r="F55">
-        <v>2.452350899146525</v>
+        <v>2.350345737165794</v>
       </c>
       <c r="G55">
-        <v>-9.502511684994037</v>
+        <v>-8.129382805576052</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>0.01605244939777065</v>
       </c>
       <c r="E56">
-        <v>-21.42515452958966</v>
+        <v>-19.64529216256292</v>
       </c>
       <c r="F56">
-        <v>2.437948903481453</v>
+        <v>2.169098949433262</v>
       </c>
       <c r="G56">
-        <v>-9.635745686415289</v>
+        <v>-7.533260316320815</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-0.03810153430094194</v>
       </c>
       <c r="E57">
-        <v>-21.07901156186536</v>
+        <v>-21.46485566121491</v>
       </c>
       <c r="F57">
-        <v>2.062763082670695</v>
+        <v>2.234621154259897</v>
       </c>
       <c r="G57">
-        <v>-9.420248179277198</v>
+        <v>-8.580183273185042</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-0.1319274444824649</v>
       </c>
       <c r="E58">
-        <v>-19.97738780391542</v>
+        <v>-19.13439425349155</v>
       </c>
       <c r="F58">
-        <v>2.266872810720493</v>
+        <v>2.101656588966938</v>
       </c>
       <c r="G58">
-        <v>-9.87842483295182</v>
+        <v>-8.966222270875273</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-0.2571149396592916</v>
       </c>
       <c r="E59">
-        <v>-20.71339615590808</v>
+        <v>-18.67818219653682</v>
       </c>
       <c r="F59">
-        <v>2.265343644494926</v>
+        <v>2.522515274898449</v>
       </c>
       <c r="G59">
-        <v>-9.674687223882779</v>
+        <v>-8.695026027765609</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-0.4060631596059212</v>
       </c>
       <c r="E60">
-        <v>-20.10078419215043</v>
+        <v>-18.07221803262243</v>
       </c>
       <c r="F60">
-        <v>2.088589921555178</v>
+        <v>2.169327578836435</v>
       </c>
       <c r="G60">
-        <v>-9.987036547791</v>
+        <v>-7.846630100134023</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-0.5704513850250785</v>
       </c>
       <c r="E61">
-        <v>-19.67484498393697</v>
+        <v>-17.99591324559319</v>
       </c>
       <c r="F61">
-        <v>1.891279433147558</v>
+        <v>1.915903482563176</v>
       </c>
       <c r="G61">
-        <v>-9.855567843568728</v>
+        <v>-8.195689730849312</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.7429484619719169</v>
       </c>
       <c r="E62">
-        <v>-20.14097892744251</v>
+        <v>-17.82276704190991</v>
       </c>
       <c r="F62">
-        <v>2.086621720606126</v>
+        <v>2.188020517648008</v>
       </c>
       <c r="G62">
-        <v>-9.744744585398484</v>
+        <v>-9.020470706917573</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.9166043124087149</v>
       </c>
       <c r="E63">
-        <v>-19.47379432341843</v>
+        <v>-16.72959794493229</v>
       </c>
       <c r="F63">
-        <v>2.105168866754807</v>
+        <v>2.051434330070009</v>
       </c>
       <c r="G63">
-        <v>-10.41460268553756</v>
+        <v>-10.10221070574907</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.084509297113659</v>
       </c>
       <c r="E64">
-        <v>-18.44397857780812</v>
+        <v>-17.52993779867792</v>
       </c>
       <c r="F64">
-        <v>1.919009860323674</v>
+        <v>2.448513901336758</v>
       </c>
       <c r="G64">
-        <v>-10.45261235608217</v>
+        <v>-9.199024940517877</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-1.240568347311557</v>
       </c>
       <c r="E65">
-        <v>-19.72491632103979</v>
+        <v>-17.14646209123438</v>
       </c>
       <c r="F65">
-        <v>1.657529062690788</v>
+        <v>2.083969288182363</v>
       </c>
       <c r="G65">
-        <v>-9.938510562148371</v>
+        <v>-9.596295559606085</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-1.377416542824159</v>
       </c>
       <c r="E66">
-        <v>-18.91425607503068</v>
+        <v>-17.99625288114376</v>
       </c>
       <c r="F66">
-        <v>1.527940922931639</v>
+        <v>1.946758511582652</v>
       </c>
       <c r="G66">
-        <v>-10.31296684773376</v>
+        <v>-9.046221733716095</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.488607334570587</v>
       </c>
       <c r="E67">
-        <v>-18.27981233808206</v>
+        <v>-17.84457164425685</v>
       </c>
       <c r="F67">
-        <v>1.848760991096665</v>
+        <v>1.6774761497502</v>
       </c>
       <c r="G67">
-        <v>-10.7837072987595</v>
+        <v>-9.536039206888443</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.566747879613975</v>
       </c>
       <c r="E68">
-        <v>-18.65746442795173</v>
+        <v>-16.33313457403476</v>
       </c>
       <c r="F68">
-        <v>1.535873369180847</v>
+        <v>1.633801306804999</v>
       </c>
       <c r="G68">
-        <v>-10.98120074320092</v>
+        <v>-9.854429259687601</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.604818469745155</v>
       </c>
       <c r="E69">
-        <v>-17.75408367663558</v>
+        <v>-16.4674083568362</v>
       </c>
       <c r="F69">
-        <v>1.492625963815491</v>
+        <v>2.172235148420261</v>
       </c>
       <c r="G69">
-        <v>-10.7582778316738</v>
+        <v>-9.139880921908885</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.597136170913811</v>
       </c>
       <c r="E70">
-        <v>-18.40934933707147</v>
+        <v>-16.71845337039942</v>
       </c>
       <c r="F70">
-        <v>1.455097606999062</v>
+        <v>1.363443724083713</v>
       </c>
       <c r="G70">
-        <v>-10.19122696543524</v>
+        <v>-8.862611137692687</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.540024014015669</v>
       </c>
       <c r="E71">
-        <v>-17.62346890083234</v>
+        <v>-16.59399731924661</v>
       </c>
       <c r="F71">
-        <v>1.079543991061461</v>
+        <v>1.635101843627394</v>
       </c>
       <c r="G71">
-        <v>-9.900750264442282</v>
+        <v>-9.279523149035732</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.430545426050827</v>
       </c>
       <c r="E72">
-        <v>-18.54393558457943</v>
+        <v>-16.22246319776131</v>
       </c>
       <c r="F72">
-        <v>1.180676053799642</v>
+        <v>1.239939114530724</v>
       </c>
       <c r="G72">
-        <v>-10.41759515959978</v>
+        <v>-10.81073143952309</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.269999626408717</v>
       </c>
       <c r="E73">
-        <v>-17.86164851973977</v>
+        <v>-16.04066760872338</v>
       </c>
       <c r="F73">
-        <v>1.108591522408029</v>
+        <v>1.393566476319114</v>
       </c>
       <c r="G73">
-        <v>-10.7035929931641</v>
+        <v>-9.88374041187812</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.056797286516463</v>
       </c>
       <c r="E74">
-        <v>-18.5001090131332</v>
+        <v>-16.23233074262402</v>
       </c>
       <c r="F74">
-        <v>1.298049087837109</v>
+        <v>1.424971541294049</v>
       </c>
       <c r="G74">
-        <v>-10.08267759380569</v>
+        <v>-9.499529054596501</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.7953094102817906</v>
       </c>
       <c r="E75">
-        <v>-17.91927787996138</v>
+        <v>-16.14619463852412</v>
       </c>
       <c r="F75">
-        <v>1.272271950996794</v>
+        <v>1.510674432787686</v>
       </c>
       <c r="G75">
-        <v>-10.64558099599311</v>
+        <v>-10.46567161788876</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.4868633112536304</v>
       </c>
       <c r="E76">
-        <v>-19.10578335471109</v>
+        <v>-17.13689795413018</v>
       </c>
       <c r="F76">
-        <v>0.8156311067339554</v>
+        <v>0.610072564096661</v>
       </c>
       <c r="G76">
-        <v>-10.13801867662729</v>
+        <v>-9.60264800454517</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.1354905109081697</v>
       </c>
       <c r="E77">
-        <v>-19.58409889329727</v>
+        <v>-16.92085804464625</v>
       </c>
       <c r="F77">
-        <v>0.8472184125375062</v>
+        <v>1.395339182561105</v>
       </c>
       <c r="G77">
-        <v>-9.443032981785983</v>
+        <v>-7.310603183740016</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.2528702392445403</v>
       </c>
       <c r="E78">
-        <v>-19.45463434989198</v>
+        <v>-16.48965222116187</v>
       </c>
       <c r="F78">
-        <v>0.6208753033965693</v>
+        <v>0.372115743968475</v>
       </c>
       <c r="G78">
-        <v>-9.427250306085053</v>
+        <v>-8.951801302121513</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.6758710722491282</v>
       </c>
       <c r="E79">
-        <v>-20.11170234298293</v>
+        <v>-19.0149874508573</v>
       </c>
       <c r="F79">
-        <v>0.8883253165340289</v>
+        <v>1.181032251782845</v>
       </c>
       <c r="G79">
-        <v>-9.25236119696665</v>
+        <v>-8.699416302212144</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>1.122484962335853</v>
       </c>
       <c r="E80">
-        <v>-20.73556756464963</v>
+        <v>-18.28502461166489</v>
       </c>
       <c r="F80">
-        <v>0.9312612557559329</v>
+        <v>0.576052343231088</v>
       </c>
       <c r="G80">
-        <v>-8.829756266217968</v>
+        <v>-8.026808538406252</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>1.59055965782467</v>
       </c>
       <c r="E81">
-        <v>-20.04422808026864</v>
+        <v>-18.19324150047742</v>
       </c>
       <c r="F81">
-        <v>0.6826267798056612</v>
+        <v>1.253660192190695</v>
       </c>
       <c r="G81">
-        <v>-8.953934096135153</v>
+        <v>-7.727295353238579</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>2.068226495996877</v>
       </c>
       <c r="E82">
-        <v>-21.82116958156043</v>
+        <v>-20.46069824933206</v>
       </c>
       <c r="F82">
-        <v>0.5386209054007868</v>
+        <v>0.4715811314922228</v>
       </c>
       <c r="G82">
-        <v>-8.708892470075822</v>
+        <v>-6.796494827363098</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>2.548877822044349</v>
       </c>
       <c r="E83">
-        <v>-21.48076871887786</v>
+        <v>-20.50602827414884</v>
       </c>
       <c r="F83">
-        <v>0.532889431340817</v>
+        <v>1.071868338707121</v>
       </c>
       <c r="G83">
-        <v>-8.657544633892071</v>
+        <v>-8.293945910446883</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>3.024370983499182</v>
       </c>
       <c r="E84">
-        <v>-22.69125246349818</v>
+        <v>-20.4731832521712</v>
       </c>
       <c r="F84">
-        <v>0.3708326028615385</v>
+        <v>1.08752116915042</v>
       </c>
       <c r="G84">
-        <v>-8.263817734088063</v>
+        <v>-7.388250010722715</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>3.483592916584658</v>
       </c>
       <c r="E85">
-        <v>-23.81534198100017</v>
+        <v>-21.68310999448859</v>
       </c>
       <c r="F85">
-        <v>0.7210381762734743</v>
+        <v>0.1136444051099592</v>
       </c>
       <c r="G85">
-        <v>-7.651266168484685</v>
+        <v>-6.885655460797889</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>3.922104338538002</v>
       </c>
       <c r="E86">
-        <v>-25.47675758188229</v>
+        <v>-22.03760346828303</v>
       </c>
       <c r="F86">
-        <v>0.1918439446690381</v>
+        <v>0.4930805790644812</v>
       </c>
       <c r="G86">
-        <v>-7.724578501787358</v>
+        <v>-6.290720773747172</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>4.326801019033023</v>
       </c>
       <c r="E87">
-        <v>-25.99495086258001</v>
+        <v>-24.83181684218388</v>
       </c>
       <c r="F87">
-        <v>0.2724242121437628</v>
+        <v>0.2017860102374378</v>
       </c>
       <c r="G87">
-        <v>-7.169435188588025</v>
+        <v>-6.660540693269066</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>4.694044742333729</v>
       </c>
       <c r="E88">
-        <v>-26.67283172221021</v>
+        <v>-24.43374133453962</v>
       </c>
       <c r="F88">
-        <v>0.2339274938334614</v>
+        <v>0.342161150315842</v>
       </c>
       <c r="G88">
-        <v>-7.718944644369792</v>
+        <v>-7.602648308638392</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>5.013958006941296</v>
       </c>
       <c r="E89">
-        <v>-27.56135455030719</v>
+        <v>-27.60888994196571</v>
       </c>
       <c r="F89">
-        <v>0.009913753829196731</v>
+        <v>0.5972386679250882</v>
       </c>
       <c r="G89">
-        <v>-7.741660541225827</v>
+        <v>-5.578351167083926</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>5.279343520337719</v>
       </c>
       <c r="E90">
-        <v>-29.473502700046</v>
+        <v>-28.70544180902705</v>
       </c>
       <c r="F90">
-        <v>-0.01572670238965636</v>
+        <v>-0.07522833293274485</v>
       </c>
       <c r="G90">
-        <v>-6.978169502666433</v>
+        <v>-5.909006426072289</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>5.48390852609709</v>
       </c>
       <c r="E91">
-        <v>-30.39750838623009</v>
+        <v>-29.60758855117612</v>
       </c>
       <c r="F91">
-        <v>-0.5579436979335035</v>
+        <v>-0.147390730860221</v>
       </c>
       <c r="G91">
-        <v>-6.791769868317498</v>
+        <v>-6.385823699426116</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>5.619337063674842</v>
       </c>
       <c r="E92">
-        <v>-32.12798095149217</v>
+        <v>-32.35997014643112</v>
       </c>
       <c r="F92">
-        <v>-0.805897255878674</v>
+        <v>-0.5976299518342251</v>
       </c>
       <c r="G92">
-        <v>-6.715346936976471</v>
+        <v>-5.990833529321721</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>5.681217376828299</v>
       </c>
       <c r="E93">
-        <v>-33.05776270627305</v>
+        <v>-31.7143750422386</v>
       </c>
       <c r="F93">
-        <v>-0.9349179639669054</v>
+        <v>-0.3328514235707939</v>
       </c>
       <c r="G93">
-        <v>-7.125115728984605</v>
+        <v>-6.20782727349092</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>5.663641670133992</v>
       </c>
       <c r="E94">
-        <v>-36.03860128674101</v>
+        <v>-35.30252047916423</v>
       </c>
       <c r="F94">
-        <v>-1.125417615588708</v>
+        <v>-1.109676149833309</v>
       </c>
       <c r="G94">
-        <v>-7.520732612406855</v>
+        <v>-6.880349725536267</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>5.565899159770474</v>
       </c>
       <c r="E95">
-        <v>-36.9839858987153</v>
+        <v>-37.53759184615301</v>
       </c>
       <c r="F95">
-        <v>-1.248380472860266</v>
+        <v>-1.000981921074972</v>
       </c>
       <c r="G95">
-        <v>-6.88063191059038</v>
+        <v>-7.443197346957176</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>5.38413729433613</v>
       </c>
       <c r="E96">
-        <v>-38.80711783488534</v>
+        <v>-38.35140843854546</v>
       </c>
       <c r="F96">
-        <v>-1.533270104928864</v>
+        <v>-1.130858332690295</v>
       </c>
       <c r="G96">
-        <v>-7.920083525963753</v>
+        <v>-6.9599357544606</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>5.126650227082946</v>
       </c>
       <c r="E97">
-        <v>-40.75039471495287</v>
+        <v>-41.54779332483051</v>
       </c>
       <c r="F97">
-        <v>-2.04051757056353</v>
+        <v>-1.382438483124921</v>
       </c>
       <c r="G97">
-        <v>-7.623274067361062</v>
+        <v>-7.739383373463572</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>4.787934344714493</v>
       </c>
       <c r="E98">
-        <v>-42.7362347222185</v>
+        <v>-42.34219182067807</v>
       </c>
       <c r="F98">
-        <v>-2.094952077703694</v>
+        <v>-1.689827402220957</v>
       </c>
       <c r="G98">
-        <v>-8.366451063245933</v>
+        <v>-7.083585307706714</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>4.398364371550624</v>
       </c>
       <c r="E99">
-        <v>-44.78911878716769</v>
+        <v>-45.44154509440077</v>
       </c>
       <c r="F99">
-        <v>-2.76608540704302</v>
+        <v>-2.071961568806396</v>
       </c>
       <c r="G99">
-        <v>-8.104373334849965</v>
+        <v>-8.325074859381335</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>3.938850289043674</v>
       </c>
       <c r="E100">
-        <v>-46.32569794508036</v>
+        <v>-47.40336154705571</v>
       </c>
       <c r="F100">
-        <v>-3.124795000212095</v>
+        <v>-1.842977624385335</v>
       </c>
       <c r="G100">
-        <v>-8.470616722872066</v>
+        <v>-7.826837771687453</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>3.480464887448221</v>
       </c>
       <c r="E101">
-        <v>-49.18821542455741</v>
+        <v>-48.66248110251841</v>
       </c>
       <c r="F101">
-        <v>-3.206226829376898</v>
+        <v>-2.242924175233172</v>
       </c>
       <c r="G101">
-        <v>-8.813970309295479</v>
+        <v>-8.619118248209414</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>2.952096270491407</v>
       </c>
       <c r="E102">
-        <v>-50.55308390504722</v>
+        <v>-50.61484096932683</v>
       </c>
       <c r="F102">
-        <v>-3.229960383834507</v>
+        <v>-2.35347394697378</v>
       </c>
       <c r="G102">
-        <v>-9.288707288180619</v>
+        <v>-8.453088437301512</v>
       </c>
     </row>
   </sheetData>
